--- a/data/input_with_dependencies_example.xlsx
+++ b/data/input_with_dependencies_example.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Plan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +24,208 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF9C5700"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF0563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAAAAA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8F8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBEEF1"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -43,14 +237,98 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -408,209 +686,3887 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AR53"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="26.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="13.1640625" customWidth="1" min="2" max="2"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="41" t="inlineStr">
         <is>
           <t>Budget Bucket</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="41" t="inlineStr">
+        <is>
+          <t>Person-months</t>
+        </is>
+      </c>
+      <c r="C1" s="42" t="inlineStr">
+        <is>
+          <t>Person-months</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>est Q26.1 without 1.1, 1.2, 1.3</t>
+        </is>
+      </c>
+      <c r="E1" s="43" t="inlineStr">
+        <is>
+          <t>estimate 1.1</t>
+        </is>
+      </c>
+      <c r="F1" s="44" t="inlineStr">
         <is>
           <t>Estimation</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="G1" s="43" t="inlineStr">
+        <is>
+          <t>MVP1.2-Q3</t>
+        </is>
+      </c>
+      <c r="H1" s="43" t="inlineStr">
+        <is>
+          <t>Allocated in Q2</t>
+        </is>
+      </c>
+      <c r="I1" s="43" t="inlineStr">
+        <is>
+          <t>estimate 1.3</t>
+        </is>
+      </c>
+      <c r="J1" s="43" t="inlineStr">
+        <is>
+          <t>estimate  2.0</t>
+        </is>
+      </c>
+      <c r="K1" s="43" t="inlineStr">
+        <is>
+          <t>Planned +used</t>
+        </is>
+      </c>
+      <c r="L1" s="43" t="inlineStr">
+        <is>
+          <t>est. left</t>
+        </is>
+      </c>
+      <c r="M1" s="43" t="inlineStr">
+        <is>
+          <t>plan left</t>
+        </is>
+      </c>
+      <c r="N1" s="27" t="inlineStr">
         <is>
           <t>Epic Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Allocation Mode</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>16.3.</t>
+        </is>
+      </c>
+      <c r="P1" s="16" t="inlineStr">
+        <is>
+          <t>23.3.</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>30.3.</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>6.4.</t>
+        </is>
+      </c>
+      <c r="S1" s="5" t="inlineStr">
+        <is>
+          <t>13.4.</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
+        <is>
+          <t>20.4.</t>
+        </is>
+      </c>
+      <c r="U1" s="5" t="inlineStr">
+        <is>
+          <t>27.4.</t>
+        </is>
+      </c>
+      <c r="V1" s="5" t="inlineStr">
+        <is>
+          <t>4.5.</t>
+        </is>
+      </c>
+      <c r="W1" s="5" t="inlineStr">
+        <is>
+          <t>11.5.</t>
+        </is>
+      </c>
+      <c r="X1" s="5" t="inlineStr">
+        <is>
+          <t>18.5.</t>
+        </is>
+      </c>
+      <c r="Y1" s="5" t="inlineStr">
+        <is>
+          <t>25.5.</t>
+        </is>
+      </c>
+      <c r="Z1" s="5" t="inlineStr">
+        <is>
+          <t>1.6.</t>
+        </is>
+      </c>
+      <c r="AA1" s="5" t="inlineStr">
+        <is>
+          <t>8.6.</t>
+        </is>
+      </c>
+      <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>15.6.</t>
+        </is>
+      </c>
+      <c r="AC1" s="5" t="inlineStr">
+        <is>
+          <t>22.6.</t>
+        </is>
+      </c>
+      <c r="AD1" s="5" t="inlineStr">
+        <is>
+          <t>29.6.</t>
+        </is>
+      </c>
+      <c r="AE1" s="5" t="inlineStr">
+        <is>
+          <t>6.7.</t>
+        </is>
+      </c>
+      <c r="AF1" s="5" t="inlineStr">
+        <is>
+          <t>13.7.</t>
+        </is>
+      </c>
+      <c r="AG1" s="5" t="inlineStr">
+        <is>
+          <t>20.7.</t>
+        </is>
+      </c>
+      <c r="AH1" s="5" t="inlineStr">
+        <is>
+          <t>27.7.</t>
+        </is>
+      </c>
+      <c r="AI1" s="5" t="inlineStr">
+        <is>
+          <t>3.8.</t>
+        </is>
+      </c>
+      <c r="AJ1" s="5" t="inlineStr">
+        <is>
+          <t>10.8.</t>
+        </is>
+      </c>
+      <c r="AK1" s="5" t="inlineStr">
+        <is>
+          <t>17.8.</t>
+        </is>
+      </c>
+      <c r="AL1" s="5" t="inlineStr">
+        <is>
+          <t>24.8.</t>
+        </is>
+      </c>
+      <c r="AM1" s="5" t="inlineStr">
+        <is>
+          <t>31.8.</t>
+        </is>
+      </c>
+      <c r="AN1" s="5" t="inlineStr">
+        <is>
+          <t>7.9.</t>
+        </is>
+      </c>
+      <c r="AO1" s="5" t="inlineStr">
+        <is>
+          <t>14.9.</t>
+        </is>
+      </c>
+      <c r="AP1" s="27" t="n"/>
+      <c r="AQ1" s="23" t="n"/>
+      <c r="AR1" s="23" t="n"/>
+      <c r="AS1" s="27" t="inlineStr">
         <is>
           <t>Depends On</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="K2" s="43" t="inlineStr">
+        <is>
+          <t>Q26.1</t>
+        </is>
+      </c>
+      <c r="O2" s="21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P2" s="21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="W2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD2" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE2" s="27" t="n"/>
+      <c r="AF2" s="23" t="n"/>
+      <c r="AG2" s="23" t="n"/>
+      <c r="AH2" s="27" t="n"/>
+      <c r="AI2" s="27" t="n"/>
+      <c r="AJ2" s="27" t="n"/>
+      <c r="AK2" s="27" t="n"/>
+      <c r="AL2" s="27" t="n"/>
+      <c r="AM2" s="27" t="n"/>
+      <c r="AN2" s="27" t="n"/>
+      <c r="AO2" s="27" t="n"/>
+      <c r="AP2" s="23" t="n"/>
+      <c r="AQ2" s="23" t="n"/>
+      <c r="AR2" s="23" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="27" t="n"/>
+      <c r="B3" s="27" t="n"/>
+      <c r="C3" s="27" t="n"/>
+      <c r="D3" s="27" t="n"/>
+      <c r="E3" s="42" t="n"/>
+      <c r="F3" s="42" t="n"/>
+      <c r="G3" s="42" t="n"/>
+      <c r="H3" s="42" t="n"/>
+      <c r="I3" s="42" t="n"/>
+      <c r="J3" s="42" t="n"/>
+      <c r="K3" s="42" t="n"/>
+      <c r="L3" s="42" t="n"/>
+      <c r="M3" s="42" t="n"/>
+      <c r="N3" s="27" t="inlineStr">
         <is>
           <t>Engineer Capacity (Bruto)</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="O3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE3" s="23" t="n"/>
+      <c r="AF3" s="23" t="n"/>
+      <c r="AG3" s="23" t="n"/>
+      <c r="AH3" s="27" t="n"/>
+      <c r="AI3" s="27" t="n"/>
+      <c r="AJ3" s="27" t="n"/>
+      <c r="AK3" s="27" t="n"/>
+      <c r="AL3" s="27" t="n"/>
+      <c r="AM3" s="27" t="n"/>
+      <c r="AN3" s="27" t="n"/>
+      <c r="AO3" s="27" t="n"/>
+      <c r="AP3" s="27" t="n"/>
+      <c r="AQ3" s="27" t="n"/>
+      <c r="AR3" s="27" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="n"/>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="42" t="n"/>
+      <c r="G4" s="42" t="n"/>
+      <c r="H4" s="42" t="n"/>
+      <c r="I4" s="42" t="n"/>
+      <c r="J4" s="42" t="n"/>
+      <c r="K4" s="42" t="n"/>
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="42" t="n"/>
+      <c r="N4" s="27" t="inlineStr">
+        <is>
+          <t>Engineer Absence</t>
+        </is>
+      </c>
+      <c r="O4" s="27" t="n"/>
+      <c r="P4" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q4" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S4" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T4" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U4" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V4" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W4" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X4" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y4" s="27" t="n"/>
+      <c r="Z4" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="27" t="n"/>
+      <c r="AB4" s="27" t="n"/>
+      <c r="AC4" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="27" t="n"/>
+      <c r="AE4" s="27" t="n"/>
+      <c r="AF4" s="27" t="n"/>
+      <c r="AG4" s="27" t="n"/>
+      <c r="AH4" s="25" t="n"/>
+      <c r="AI4" s="27" t="n"/>
+      <c r="AJ4" s="27" t="n"/>
+      <c r="AK4" s="27" t="n"/>
+      <c r="AL4" s="27" t="n"/>
+      <c r="AM4" s="27" t="n"/>
+      <c r="AN4" s="27" t="n"/>
+      <c r="AO4" s="27" t="n"/>
+      <c r="AP4" s="25" t="n"/>
+      <c r="AQ4" s="23" t="n"/>
+      <c r="AR4" s="23" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="n"/>
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="42" t="n"/>
+      <c r="F5" s="42" t="n"/>
+      <c r="G5" s="42" t="n"/>
+      <c r="H5" s="42" t="n"/>
+      <c r="I5" s="42" t="n"/>
+      <c r="J5" s="42" t="n"/>
+      <c r="K5" s="42" t="n"/>
+      <c r="L5" s="42" t="n"/>
+      <c r="M5" s="42" t="n"/>
+      <c r="N5" s="27" t="inlineStr">
+        <is>
+          <t>Holiday team members</t>
+        </is>
+      </c>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nev 2d? </t>
+        </is>
+      </c>
+      <c r="Q5" s="27" t="inlineStr">
+        <is>
+          <t>Nev = 5</t>
+        </is>
+      </c>
+      <c r="R5" s="27" t="inlineStr">
+        <is>
+          <t>Easter</t>
+        </is>
+      </c>
+      <c r="S5" s="27" t="inlineStr">
+        <is>
+          <t>Easter</t>
+        </is>
+      </c>
+      <c r="T5" s="27" t="inlineStr">
+        <is>
+          <t>Nev = 3</t>
+        </is>
+      </c>
+      <c r="U5" s="27" t="inlineStr">
+        <is>
+          <t>Arni = 1, Labour day</t>
+        </is>
+      </c>
+      <c r="V5" s="27" t="inlineStr">
+        <is>
+          <t>Arni = 1</t>
+        </is>
+      </c>
+      <c r="W5" s="25" t="inlineStr">
+        <is>
+          <t>Ascension Day</t>
+        </is>
+      </c>
+      <c r="X5" s="27" t="inlineStr">
+        <is>
+          <t>Some public holiday</t>
+        </is>
+      </c>
+      <c r="Y5" s="27" t="n"/>
+      <c r="Z5" s="27" t="inlineStr">
+        <is>
+          <t>Nev = 5</t>
+        </is>
+      </c>
+      <c r="AA5" s="27" t="n"/>
+      <c r="AB5" s="27" t="n"/>
+      <c r="AC5" s="27" t="inlineStr">
+        <is>
+          <t>Arni = 5</t>
+        </is>
+      </c>
+      <c r="AD5" s="27" t="n"/>
+      <c r="AE5" s="25" t="n"/>
+      <c r="AF5" s="23" t="n"/>
+      <c r="AG5" s="23" t="n"/>
+      <c r="AH5" s="27" t="n"/>
+      <c r="AI5" s="27" t="n"/>
+      <c r="AJ5" s="27" t="n"/>
+      <c r="AK5" s="27" t="n"/>
+      <c r="AL5" s="27" t="n"/>
+      <c r="AM5" s="27" t="n"/>
+      <c r="AN5" s="27" t="n"/>
+      <c r="AO5" s="27" t="n"/>
+      <c r="AP5" s="27" t="n"/>
+      <c r="AQ5" s="27" t="n"/>
+      <c r="AR5" s="27" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="n"/>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Line management</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="42" t="n"/>
+      <c r="F6" s="42" t="n"/>
+      <c r="G6" s="42" t="n"/>
+      <c r="H6" s="42" t="n"/>
+      <c r="I6" s="42" t="n"/>
+      <c r="J6" s="42" t="n"/>
+      <c r="K6" s="42" t="n"/>
+      <c r="L6" s="42" t="n"/>
+      <c r="M6" s="42" t="n"/>
+      <c r="N6" s="27" t="inlineStr">
+        <is>
+          <t>Management Capacity (Bruto)</t>
+        </is>
+      </c>
+      <c r="O6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="S6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="U6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="V6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="W6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="X6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Y6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AA6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AD6" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AE6" s="27" t="n"/>
+      <c r="AF6" s="27" t="n"/>
+      <c r="AG6" s="27" t="n"/>
+      <c r="AH6" s="27" t="n"/>
+      <c r="AI6" s="27" t="n"/>
+      <c r="AJ6" s="27" t="n"/>
+      <c r="AK6" s="27" t="n"/>
+      <c r="AL6" s="27" t="n"/>
+      <c r="AM6" s="27" t="n"/>
+      <c r="AN6" s="27" t="n"/>
+      <c r="AO6" s="27" t="n"/>
+      <c r="AP6" s="27" t="n"/>
+      <c r="AQ6" s="25" t="n"/>
+      <c r="AR6" s="25" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="n"/>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Line management absence</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="42" t="n"/>
+      <c r="F7" s="42" t="n"/>
+      <c r="G7" s="42" t="n"/>
+      <c r="H7" s="42" t="n"/>
+      <c r="I7" s="42" t="n"/>
+      <c r="J7" s="42" t="n"/>
+      <c r="K7" s="42" t="n"/>
+      <c r="L7" s="42" t="n"/>
+      <c r="M7" s="42" t="n"/>
+      <c r="N7" s="27" t="inlineStr">
+        <is>
+          <t>Management Absence</t>
+        </is>
+      </c>
+      <c r="O7" s="27" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="P7" s="27" t="n"/>
+      <c r="Q7" s="27" t="n"/>
+      <c r="R7" s="27" t="n"/>
+      <c r="S7" s="27" t="n"/>
+      <c r="T7" s="27" t="n"/>
+      <c r="U7" s="27" t="n"/>
+      <c r="V7" s="27" t="n"/>
+      <c r="W7" s="27" t="n"/>
+      <c r="X7" s="27" t="n"/>
+      <c r="Y7" s="27" t="n"/>
+      <c r="Z7" s="27" t="n"/>
+      <c r="AA7" s="27" t="n"/>
+      <c r="AB7" s="27" t="n"/>
+      <c r="AC7" s="27" t="n"/>
+      <c r="AD7" s="27" t="n"/>
+      <c r="AE7" s="27" t="n"/>
+      <c r="AF7" s="25" t="n"/>
+      <c r="AG7" s="25" t="n"/>
+      <c r="AH7" s="27" t="n"/>
+      <c r="AI7" s="27" t="n"/>
+      <c r="AJ7" s="27" t="n"/>
+      <c r="AK7" s="27" t="n"/>
+      <c r="AL7" s="27" t="n"/>
+      <c r="AM7" s="27" t="n"/>
+      <c r="AN7" s="27" t="n"/>
+      <c r="AO7" s="27" t="n"/>
+      <c r="AP7" s="27" t="n"/>
+      <c r="AQ7" s="27" t="n"/>
+      <c r="AR7" s="27" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="n"/>
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="42" t="n"/>
+      <c r="F8" s="42" t="n"/>
+      <c r="G8" s="42" t="n"/>
+      <c r="H8" s="42" t="n"/>
+      <c r="I8" s="42" t="n"/>
+      <c r="J8" s="42" t="n"/>
+      <c r="K8" s="42" t="n"/>
+      <c r="L8" s="42" t="n"/>
+      <c r="M8" s="42" t="n"/>
+      <c r="N8" s="27" t="n"/>
+      <c r="O8" s="27" t="n"/>
+      <c r="P8" s="27" t="n"/>
+      <c r="Q8" s="27" t="n"/>
+      <c r="R8" s="27" t="n"/>
+      <c r="S8" s="27" t="n"/>
+      <c r="T8" s="27" t="n"/>
+      <c r="U8" s="27" t="n"/>
+      <c r="V8" s="27" t="n"/>
+      <c r="W8" s="27" t="n"/>
+      <c r="X8" s="27" t="n"/>
+      <c r="Y8" s="27" t="n"/>
+      <c r="Z8" s="27" t="n"/>
+      <c r="AA8" s="27" t="n"/>
+      <c r="AB8" s="27" t="n"/>
+      <c r="AC8" s="27" t="n"/>
+      <c r="AD8" s="27" t="n"/>
+      <c r="AE8" s="27" t="n"/>
+      <c r="AF8" s="27" t="n"/>
+      <c r="AG8" s="27" t="n"/>
+      <c r="AH8" s="21" t="n"/>
+      <c r="AI8" s="21" t="n"/>
+      <c r="AJ8" s="21" t="n"/>
+      <c r="AK8" s="21" t="n"/>
+      <c r="AL8" s="21" t="n"/>
+      <c r="AM8" s="21" t="n"/>
+      <c r="AN8" s="21" t="n"/>
+      <c r="AO8" s="21" t="n"/>
+      <c r="AP8" s="27" t="n"/>
+      <c r="AQ8" s="27" t="n"/>
+      <c r="AR8" s="27" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="22" t="n"/>
+      <c r="K9" s="22" t="n"/>
+      <c r="L9" s="22" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="27" t="inlineStr">
+        <is>
+          <t>Capacity incl. EM</t>
+        </is>
+      </c>
+      <c r="O9" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q9" s="21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R9" s="21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S9" s="21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T9" s="21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U9" s="21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V9" s="21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W9" s="21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X9" s="21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y9" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z9" s="21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA9" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB9" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC9" s="21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD9" s="21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE9" s="27" t="n"/>
+      <c r="AF9" s="27" t="n"/>
+      <c r="AG9" s="27" t="n"/>
+      <c r="AH9" s="21" t="n"/>
+      <c r="AI9" s="21" t="n"/>
+      <c r="AJ9" s="21" t="n"/>
+      <c r="AK9" s="21" t="n"/>
+      <c r="AL9" s="21" t="n"/>
+      <c r="AM9" s="21" t="n"/>
+      <c r="AN9" s="21" t="n"/>
+      <c r="AO9" s="21" t="n"/>
+      <c r="AP9" s="27" t="n"/>
+      <c r="AQ9" s="27" t="n"/>
+      <c r="AR9" s="27" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
+      <c r="M10" s="22" t="n"/>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>Engineer Net capacity</t>
+        </is>
+      </c>
+      <c r="O10" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" s="21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S10" s="21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T10" s="21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U10" s="21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" s="21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W10" s="21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X10" s="21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE10" s="27" t="n"/>
+      <c r="AF10" s="27" t="n"/>
+      <c r="AG10" s="27" t="n"/>
+      <c r="AH10" s="21" t="n"/>
+      <c r="AI10" s="21" t="n"/>
+      <c r="AJ10" s="21" t="n"/>
+      <c r="AK10" s="21" t="n"/>
+      <c r="AL10" s="21" t="n"/>
+      <c r="AM10" s="21" t="n"/>
+      <c r="AN10" s="21" t="n"/>
+      <c r="AO10" s="21" t="n"/>
+      <c r="AP10" s="27" t="n"/>
+      <c r="AQ10" s="27" t="n"/>
+      <c r="AR10" s="27" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="22" t="n"/>
+      <c r="L11" s="22" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="21" t="n"/>
+      <c r="O11" s="21" t="n"/>
+      <c r="P11" s="21" t="n"/>
+      <c r="Q11" s="21" t="n"/>
+      <c r="R11" s="21" t="n"/>
+      <c r="S11" s="21" t="n"/>
+      <c r="T11" s="21" t="n"/>
+      <c r="U11" s="21" t="n"/>
+      <c r="V11" s="21" t="n"/>
+      <c r="W11" s="21" t="n"/>
+      <c r="X11" s="21" t="n"/>
+      <c r="Y11" s="21" t="n"/>
+      <c r="Z11" s="21" t="n"/>
+      <c r="AA11" s="21" t="n"/>
+      <c r="AB11" s="21" t="n"/>
+      <c r="AC11" s="21" t="n"/>
+      <c r="AD11" s="21" t="n"/>
+      <c r="AE11" s="27" t="n"/>
+      <c r="AF11" s="27" t="n"/>
+      <c r="AG11" s="27" t="n"/>
+      <c r="AH11" s="27" t="n"/>
+      <c r="AI11" s="27" t="n"/>
+      <c r="AJ11" s="27" t="n"/>
+      <c r="AK11" s="27" t="n"/>
+      <c r="AL11" s="27" t="n"/>
+      <c r="AM11" s="27" t="n"/>
+      <c r="AN11" s="27" t="n"/>
+      <c r="AO11" s="27" t="n"/>
+      <c r="AP11" s="27" t="n"/>
+      <c r="AQ11" s="27" t="n"/>
+      <c r="AR11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Overhead</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="42" t="n"/>
+      <c r="F12" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="42" t="n"/>
+      <c r="H12" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="42" t="n"/>
+      <c r="J12" s="42" t="n"/>
+      <c r="K12" s="42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L12" s="42" t="n"/>
+      <c r="M12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="27" t="inlineStr">
+        <is>
+          <t>Onoboard Omar/ Nam/ Reboot</t>
+        </is>
+      </c>
+      <c r="O12" s="27" t="n"/>
+      <c r="P12" s="27" t="n"/>
+      <c r="Q12" s="27" t="n"/>
+      <c r="R12" s="27" t="n"/>
+      <c r="S12" s="27" t="n"/>
+      <c r="T12" s="27" t="n"/>
+      <c r="U12" s="27" t="n"/>
+      <c r="V12" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W12" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X12" s="27" t="n"/>
+      <c r="Y12" s="27" t="n"/>
+      <c r="Z12" s="27" t="n"/>
+      <c r="AA12" s="27" t="n"/>
+      <c r="AB12" s="27" t="n"/>
+      <c r="AC12" s="27" t="n"/>
+      <c r="AD12" s="27" t="n"/>
+      <c r="AE12" s="27" t="n"/>
+      <c r="AF12" s="27" t="n"/>
+      <c r="AG12" s="27" t="n"/>
+      <c r="AH12" s="27" t="n"/>
+      <c r="AI12" s="27" t="n"/>
+      <c r="AJ12" s="27" t="n"/>
+      <c r="AK12" s="27" t="n"/>
+      <c r="AL12" s="27" t="n"/>
+      <c r="AM12" s="27" t="n"/>
+      <c r="AN12" s="27" t="n"/>
+      <c r="AO12" s="27" t="n"/>
+      <c r="AP12" s="27" t="n"/>
+      <c r="AQ12" s="27" t="n"/>
+      <c r="AR12" s="27" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E13" s="42" t="n"/>
+      <c r="F13" s="42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G13" s="42" t="n"/>
+      <c r="H13" s="42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I13" s="42" t="n"/>
+      <c r="J13" s="42" t="n"/>
+      <c r="K13" s="42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L13" s="42" t="n"/>
+      <c r="M13" s="16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N13" s="27" t="inlineStr">
+        <is>
+          <t>bugs in production</t>
+        </is>
+      </c>
+      <c r="O13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AA13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD13" s="27" t="n"/>
+      <c r="AE13" s="27" t="n"/>
+      <c r="AF13" s="27" t="n"/>
+      <c r="AG13" s="27" t="n"/>
+      <c r="AH13" s="27" t="n"/>
+      <c r="AI13" s="27" t="n"/>
+      <c r="AJ13" s="27" t="n"/>
+      <c r="AK13" s="27" t="n"/>
+      <c r="AL13" s="27" t="n"/>
+      <c r="AM13" s="27" t="n"/>
+      <c r="AN13" s="27" t="n"/>
+      <c r="AO13" s="27" t="n"/>
+      <c r="AP13" s="27" t="n"/>
+      <c r="AQ13" s="27" t="n"/>
+      <c r="AR13" s="27" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Operational Excellence</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>KTLO &amp; OpEx (Nevena)</t>
+        </is>
+      </c>
+      <c r="O14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q14" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R14" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S14" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T14" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U14" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V14" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W14" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X14" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y14" s="27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Z14" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA14" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB14" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC14" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD14" s="27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE14" s="27" t="n"/>
+      <c r="AF14" s="27" t="n"/>
+      <c r="AG14" s="27" t="n"/>
+      <c r="AH14" s="27" t="n"/>
+      <c r="AI14" s="27" t="n"/>
+      <c r="AJ14" s="27" t="n"/>
+      <c r="AK14" s="27" t="n"/>
+      <c r="AL14" s="27" t="n"/>
+      <c r="AM14" s="27" t="n"/>
+      <c r="AN14" s="27" t="n"/>
+      <c r="AO14" s="27" t="n"/>
+      <c r="AP14" s="27" t="n"/>
+      <c r="AQ14" s="10" t="n"/>
+      <c r="AR14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>KTLO</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NAV-170423</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="42" t="n"/>
+      <c r="F15" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="42" t="n"/>
+      <c r="H15" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="42" t="n"/>
+      <c r="J15" s="42" t="n"/>
+      <c r="K15" s="42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="42" t="n"/>
+      <c r="M15" s="16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Data of Customer Fleets are ingested and visual in dashboard. (Nevena + intern?)</t>
+        </is>
+      </c>
+      <c r="O15" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P15" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB15" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AC15" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD15" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE15" s="27" t="n"/>
+      <c r="AF15" s="10" t="n"/>
+      <c r="AG15" s="10" t="n"/>
+      <c r="AH15" s="27" t="n"/>
+      <c r="AI15" s="27" t="n"/>
+      <c r="AJ15" s="27" t="n"/>
+      <c r="AK15" s="27" t="n"/>
+      <c r="AL15" s="27" t="n"/>
+      <c r="AM15" s="27" t="n"/>
+      <c r="AN15" s="27" t="n"/>
+      <c r="AO15" s="27" t="n"/>
+      <c r="AP15" s="27" t="n"/>
+      <c r="AQ15" s="27" t="n"/>
+      <c r="AR15" s="27" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Critical Technical Debt</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>KTLO</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="42" t="n"/>
+      <c r="F16" s="42" t="n"/>
+      <c r="G16" s="42" t="n"/>
+      <c r="H16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="42" t="inlineStr">
+        <is>
+          <t>2?</t>
+        </is>
+      </c>
+      <c r="J16" s="42" t="n"/>
+      <c r="K16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="42" t="n"/>
+      <c r="M16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Separate data and metrics for production cars from test data</t>
+        </is>
+      </c>
+      <c r="O16" s="27" t="n"/>
+      <c r="P16" s="27" t="n"/>
+      <c r="Q16" s="27" t="n"/>
+      <c r="R16" s="27" t="n"/>
+      <c r="S16" s="27" t="n"/>
+      <c r="T16" s="27" t="n"/>
+      <c r="U16" s="27" t="n"/>
+      <c r="V16" s="27" t="n"/>
+      <c r="W16" s="27" t="n"/>
+      <c r="X16" s="27" t="n"/>
+      <c r="Y16" s="27" t="n"/>
+      <c r="Z16" s="27" t="n"/>
+      <c r="AA16" s="27" t="n"/>
+      <c r="AB16" s="27" t="n"/>
+      <c r="AC16" s="27" t="n"/>
+      <c r="AD16" s="27" t="n"/>
+      <c r="AE16" s="27" t="n"/>
+      <c r="AF16" s="27" t="n"/>
+      <c r="AG16" s="27" t="n"/>
+      <c r="AH16" s="27" t="n"/>
+      <c r="AI16" s="27" t="n"/>
+      <c r="AJ16" s="27" t="n"/>
+      <c r="AK16" s="27" t="n"/>
+      <c r="AL16" s="27" t="n"/>
+      <c r="AM16" s="27" t="n"/>
+      <c r="AN16" s="27" t="n"/>
+      <c r="AO16" s="27" t="n"/>
+      <c r="AP16" s="27" t="n"/>
+      <c r="AQ16" s="27" t="n"/>
+      <c r="AR16" s="27" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Security &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>KTLO</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>NAV-180094</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E17" s="42" t="n"/>
+      <c r="F17" s="14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G17" s="42" t="n"/>
+      <c r="H17" s="42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I17" s="42" t="n"/>
+      <c r="J17" s="42" t="n"/>
+      <c r="K17" s="42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L17" s="42" t="n"/>
+      <c r="M17" s="16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>DATA storage and usage according to legal regulations.  Database investigation and cleanup (Nevena / intern?)</t>
+        </is>
+      </c>
+      <c r="O17" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P17" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q17" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R17" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S17" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T17" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U17" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V17" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X17" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y17" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z17" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AA17" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB17" s="27" t="n"/>
+      <c r="AC17" s="27" t="n"/>
+      <c r="AD17" s="27" t="n"/>
+      <c r="AE17" s="27" t="n"/>
+      <c r="AF17" s="27" t="n"/>
+      <c r="AG17" s="27" t="n"/>
+      <c r="AH17" s="27" t="n"/>
+      <c r="AI17" s="27" t="n"/>
+      <c r="AJ17" s="27" t="n"/>
+      <c r="AK17" s="27" t="n"/>
+      <c r="AL17" s="27" t="n"/>
+      <c r="AM17" s="27" t="n"/>
+      <c r="AN17" s="27" t="n"/>
+      <c r="AO17" s="27" t="n"/>
+      <c r="AP17" s="27" t="n"/>
+      <c r="AQ17" s="23" t="n"/>
+      <c r="AR17" s="23" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="42" t="n"/>
+      <c r="F18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="42" t="n"/>
+      <c r="H18" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="42" t="n"/>
+      <c r="J18" s="42" t="n"/>
+      <c r="K18" s="42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L18" s="42" t="n"/>
+      <c r="M18" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Onboard JLR to our metrics to ADP and Developer portal ( Arni )</t>
+        </is>
+      </c>
+      <c r="O18" s="27" t="n"/>
+      <c r="P18" s="27" t="n"/>
+      <c r="Q18" s="27" t="n"/>
+      <c r="R18" s="27" t="n"/>
+      <c r="S18" s="27" t="n"/>
+      <c r="T18" s="27" t="n"/>
+      <c r="U18" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V18" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X18" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y18" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z18" s="27" t="n"/>
+      <c r="AA18" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB18" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC18" s="27" t="n"/>
+      <c r="AD18" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE18" s="27" t="n"/>
+      <c r="AF18" s="23" t="n"/>
+      <c r="AG18" s="23" t="n"/>
+      <c r="AH18" s="27" t="n"/>
+      <c r="AI18" s="27" t="n"/>
+      <c r="AJ18" s="27" t="n"/>
+      <c r="AK18" s="27" t="n"/>
+      <c r="AL18" s="27" t="n"/>
+      <c r="AM18" s="27" t="n"/>
+      <c r="AN18" s="27" t="n"/>
+      <c r="AO18" s="27" t="n"/>
+      <c r="AP18" s="27" t="n"/>
+      <c r="AQ18" s="27" t="n"/>
+      <c r="AR18" s="27" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="42" t="n"/>
+      <c r="F19" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="42" t="n"/>
+      <c r="H19" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="42" t="n"/>
+      <c r="J19" s="42" t="n"/>
+      <c r="K19" s="42" t="n"/>
+      <c r="L19" s="42" t="n"/>
+      <c r="M19" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Q26.2 Support the DATA Flywheel  loop</t>
+        </is>
+      </c>
+      <c r="O19" s="27" t="n"/>
+      <c r="P19" s="27" t="n"/>
+      <c r="Q19" s="27" t="n"/>
+      <c r="R19" s="27" t="n"/>
+      <c r="S19" s="27" t="n"/>
+      <c r="T19" s="27" t="n"/>
+      <c r="U19" s="27" t="n"/>
+      <c r="V19" s="27" t="n"/>
+      <c r="W19" s="27" t="n"/>
+      <c r="X19" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y19" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z19" s="27" t="n"/>
+      <c r="AA19" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB19" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC19" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD19" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE19" s="27" t="n"/>
+      <c r="AF19" s="27" t="n"/>
+      <c r="AG19" s="27" t="n"/>
+      <c r="AH19" s="27" t="n"/>
+      <c r="AI19" s="27" t="n"/>
+      <c r="AJ19" s="27" t="n"/>
+      <c r="AK19" s="27" t="n"/>
+      <c r="AL19" s="27" t="n"/>
+      <c r="AM19" s="27" t="n"/>
+      <c r="AN19" s="27" t="n"/>
+      <c r="AO19" s="27" t="n"/>
+      <c r="AP19" s="27" t="n"/>
+      <c r="AQ19" s="27" t="n"/>
+      <c r="AR19" s="27" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Other features</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-21982</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="42" t="n"/>
+      <c r="F20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="42" t="n"/>
+      <c r="H20" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="42" t="n"/>
+      <c r="J20" s="42" t="n"/>
+      <c r="K20" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="42" t="n"/>
+      <c r="M20" s="16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>[NavSDK] Measure EV Quality Metrics Suite(Omar)</t>
+        </is>
+      </c>
+      <c r="O20" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P20" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q20" s="27" t="n"/>
+      <c r="R20" s="27" t="n"/>
+      <c r="S20" s="27" t="n"/>
+      <c r="T20" s="27" t="n"/>
+      <c r="U20" s="27" t="n"/>
+      <c r="V20" s="27" t="n"/>
+      <c r="W20" s="27" t="n"/>
+      <c r="X20" s="27" t="n"/>
+      <c r="Y20" s="27" t="n"/>
+      <c r="Z20" s="27" t="n"/>
+      <c r="AA20" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB20" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC20" s="27" t="n"/>
+      <c r="AD20" s="27" t="n"/>
+      <c r="AE20" s="27" t="n"/>
+      <c r="AF20" s="27" t="n"/>
+      <c r="AG20" s="27" t="n"/>
+      <c r="AH20" s="27" t="n"/>
+      <c r="AI20" s="27" t="n"/>
+      <c r="AJ20" s="27" t="n"/>
+      <c r="AK20" s="27" t="n"/>
+      <c r="AL20" s="27" t="n"/>
+      <c r="AM20" s="27" t="n"/>
+      <c r="AN20" s="27" t="n"/>
+      <c r="AO20" s="27" t="n"/>
+      <c r="AP20" s="27" t="n"/>
+      <c r="AQ20" s="27" t="n"/>
+      <c r="AR20" s="27" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Critical Technical Debt</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Solution design</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="42" t="n"/>
+      <c r="F21" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G21" s="42" t="n"/>
+      <c r="H21" s="42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I21" s="42" t="n"/>
+      <c r="J21" s="42" t="n"/>
+      <c r="K21" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="42" t="n"/>
+      <c r="M21" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>SD Separate data and metrics for production cars from test data</t>
+        </is>
+      </c>
+      <c r="O21" s="27" t="n"/>
+      <c r="P21" s="27" t="n"/>
+      <c r="Q21" s="27" t="n"/>
+      <c r="R21" s="27" t="n"/>
+      <c r="S21" s="27" t="n"/>
+      <c r="T21" s="27" t="n"/>
+      <c r="U21" s="27" t="n"/>
+      <c r="V21" s="27" t="n"/>
+      <c r="W21" s="27" t="n"/>
+      <c r="X21" s="27" t="n"/>
+      <c r="Y21" s="27" t="n"/>
+      <c r="Z21" s="27" t="n"/>
+      <c r="AA21" s="27" t="n"/>
+      <c r="AB21" s="27" t="n"/>
+      <c r="AC21" s="27" t="n"/>
+      <c r="AD21" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE21" s="27" t="n"/>
+      <c r="AF21" s="27" t="n"/>
+      <c r="AG21" s="27" t="n"/>
+      <c r="AH21" s="27" t="n"/>
+      <c r="AI21" s="27" t="n"/>
+      <c r="AJ21" s="27" t="n"/>
+      <c r="AK21" s="27" t="n"/>
+      <c r="AL21" s="27" t="n"/>
+      <c r="AM21" s="27" t="n"/>
+      <c r="AN21" s="27" t="n"/>
+      <c r="AO21" s="27" t="n"/>
+      <c r="AP21" s="27" t="n"/>
+      <c r="AQ21" s="27" t="n"/>
+      <c r="AR21" s="27" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Customer Support</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Other features</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G22" s="42" t="n"/>
+      <c r="H22" s="42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I22" s="42" t="n"/>
+      <c r="J22" s="42" t="n"/>
+      <c r="K22" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L22" s="42" t="n"/>
+      <c r="M22" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t>MXNavi onboard AI powered EV Range via direct API's</t>
+        </is>
+      </c>
+      <c r="O22" s="27" t="n"/>
+      <c r="P22" s="27" t="n"/>
+      <c r="Q22" s="27" t="n"/>
+      <c r="R22" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S22" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T22" s="27" t="n"/>
+      <c r="U22" s="27" t="n"/>
+      <c r="V22" s="27" t="n"/>
+      <c r="W22" s="27" t="n"/>
+      <c r="X22" s="27" t="n"/>
+      <c r="Y22" s="27" t="n"/>
+      <c r="Z22" s="27" t="n"/>
+      <c r="AA22" s="27" t="n"/>
+      <c r="AB22" s="27" t="n"/>
+      <c r="AC22" s="27" t="n"/>
+      <c r="AD22" s="27" t="n"/>
+      <c r="AE22" s="27" t="n"/>
+      <c r="AF22" s="27" t="n"/>
+      <c r="AG22" s="27" t="n"/>
+      <c r="AH22" s="27" t="n"/>
+      <c r="AI22" s="27" t="n"/>
+      <c r="AJ22" s="27" t="n"/>
+      <c r="AK22" s="27" t="n"/>
+      <c r="AL22" s="27" t="n"/>
+      <c r="AM22" s="27" t="n"/>
+      <c r="AN22" s="27" t="n"/>
+      <c r="AO22" s="27" t="n"/>
+      <c r="AP22" s="27" t="n"/>
+      <c r="AQ22" s="27" t="n"/>
+      <c r="AR22" s="27" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Solution design</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="42" t="n"/>
+      <c r="H23" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="42" t="n"/>
+      <c r="J23" s="42" t="n"/>
+      <c r="K23" s="42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L23" s="42" t="n"/>
+      <c r="M23" s="42" t="n"/>
+      <c r="N23" s="18" t="inlineStr">
+        <is>
+          <t>SD WL MVP 1.2: EV Metrics Dashboard Extension (Arni)</t>
+        </is>
+      </c>
+      <c r="O23" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P23" s="27" t="n"/>
+      <c r="Q23" s="27" t="n"/>
+      <c r="R23" s="27" t="n"/>
+      <c r="S23" s="27" t="n"/>
+      <c r="T23" s="27" t="n"/>
+      <c r="U23" s="27" t="n"/>
+      <c r="V23" s="27" t="n"/>
+      <c r="W23" s="27" t="n"/>
+      <c r="X23" s="27" t="n"/>
+      <c r="Y23" s="27" t="n"/>
+      <c r="Z23" s="27" t="n"/>
+      <c r="AA23" s="27" t="n"/>
+      <c r="AB23" s="27" t="n"/>
+      <c r="AC23" s="27" t="n"/>
+      <c r="AD23" s="27" t="n"/>
+      <c r="AE23" s="27" t="n"/>
+      <c r="AF23" s="27" t="n"/>
+      <c r="AG23" s="27" t="n"/>
+      <c r="AH23" s="27" t="n"/>
+      <c r="AI23" s="27" t="n"/>
+      <c r="AJ23" s="27" t="n"/>
+      <c r="AK23" s="27" t="n"/>
+      <c r="AL23" s="27" t="n"/>
+      <c r="AM23" s="27" t="n"/>
+      <c r="AN23" s="27" t="n"/>
+      <c r="AO23" s="27" t="n"/>
+      <c r="AP23" s="27" t="n"/>
+      <c r="AQ23" s="27" t="n"/>
+      <c r="AR23" s="27" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Solution design</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="27" t="n"/>
+      <c r="J24" s="42" t="n"/>
+      <c r="K24" s="42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L24" s="42" t="n"/>
+      <c r="M24" s="42" t="n"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>SD WL MVP 1.2: Feature generation capability and process (Omar)</t>
+        </is>
+      </c>
+      <c r="O24" s="27" t="n"/>
+      <c r="P24" s="27" t="n"/>
+      <c r="Q24" s="27" t="n"/>
+      <c r="R24" s="27" t="n"/>
+      <c r="S24" s="27" t="n"/>
+      <c r="T24" s="27" t="n"/>
+      <c r="U24" s="27" t="n"/>
+      <c r="V24" s="27" t="n"/>
+      <c r="W24" s="27" t="n"/>
+      <c r="X24" s="27" t="n"/>
+      <c r="Y24" s="27" t="n"/>
+      <c r="Z24" s="27" t="n"/>
+      <c r="AA24" s="27" t="n"/>
+      <c r="AB24" s="27" t="n"/>
+      <c r="AC24" s="27" t="n"/>
+      <c r="AD24" s="27" t="n"/>
+      <c r="AE24" s="27" t="n"/>
+      <c r="AF24" s="27" t="n"/>
+      <c r="AG24" s="27" t="n"/>
+      <c r="AH24" s="27" t="n"/>
+      <c r="AI24" s="27" t="n"/>
+      <c r="AJ24" s="27" t="n"/>
+      <c r="AK24" s="27" t="n"/>
+      <c r="AL24" s="27" t="n"/>
+      <c r="AM24" s="27" t="n"/>
+      <c r="AN24" s="27" t="n"/>
+      <c r="AO24" s="27" t="n"/>
+      <c r="AP24" s="27" t="n"/>
+      <c r="AQ24" s="27" t="n"/>
+      <c r="AR24" s="27" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Solution design</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="27" t="n"/>
+      <c r="J25" s="42" t="n"/>
+      <c r="K25" s="42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L25" s="42" t="n"/>
+      <c r="M25" s="42" t="n"/>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>SD WL MVP1 .2: Define process to create prod-grade Fusion Model + create the first prod-grade version (Omar)</t>
+        </is>
+      </c>
+      <c r="O25" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P25" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q25" s="27" t="n"/>
+      <c r="R25" s="27" t="n"/>
+      <c r="S25" s="27" t="n"/>
+      <c r="T25" s="27" t="n"/>
+      <c r="U25" s="27" t="n"/>
+      <c r="V25" s="27" t="n"/>
+      <c r="W25" s="27" t="n"/>
+      <c r="X25" s="27" t="n"/>
+      <c r="Y25" s="27" t="n"/>
+      <c r="Z25" s="27" t="n"/>
+      <c r="AA25" s="27" t="n"/>
+      <c r="AB25" s="27" t="n"/>
+      <c r="AC25" s="27" t="n"/>
+      <c r="AD25" s="27" t="n"/>
+      <c r="AE25" s="27" t="n"/>
+      <c r="AF25" s="27" t="n"/>
+      <c r="AG25" s="27" t="n"/>
+      <c r="AH25" s="27" t="n"/>
+      <c r="AI25" s="27" t="n"/>
+      <c r="AJ25" s="27" t="n"/>
+      <c r="AK25" s="27" t="n"/>
+      <c r="AL25" s="27" t="n"/>
+      <c r="AM25" s="27" t="n"/>
+      <c r="AN25" s="27" t="n"/>
+      <c r="AO25" s="27" t="n"/>
+      <c r="AP25" s="27" t="n"/>
+      <c r="AQ25" s="27" t="n"/>
+      <c r="AR25" s="27" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Solution design</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="42" t="n"/>
+      <c r="H26" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="42" t="n"/>
+      <c r="J26" s="42" t="n"/>
+      <c r="K26" s="42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L26" s="42" t="n"/>
+      <c r="M26" s="42" t="n"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>SD MVP 1.2: WP 39: Add Consistency Check to Fusion Model Pipeline(Arni)</t>
+        </is>
+      </c>
+      <c r="O26" s="27" t="n"/>
+      <c r="P26" s="27" t="n"/>
+      <c r="Q26" s="27" t="n"/>
+      <c r="R26" s="27" t="n"/>
+      <c r="S26" s="27" t="n"/>
+      <c r="T26" s="27" t="n"/>
+      <c r="U26" s="27" t="n"/>
+      <c r="V26" s="27" t="n"/>
+      <c r="W26" s="27" t="n"/>
+      <c r="X26" s="27" t="n"/>
+      <c r="Y26" s="27" t="n"/>
+      <c r="Z26" s="27" t="n"/>
+      <c r="AA26" s="27" t="n"/>
+      <c r="AB26" s="27" t="n"/>
+      <c r="AC26" s="27" t="n"/>
+      <c r="AD26" s="27" t="n"/>
+      <c r="AE26" s="27" t="n"/>
+      <c r="AF26" s="27" t="n"/>
+      <c r="AG26" s="27" t="n"/>
+      <c r="AH26" s="27" t="n"/>
+      <c r="AI26" s="27" t="n"/>
+      <c r="AJ26" s="27" t="n"/>
+      <c r="AK26" s="27" t="n"/>
+      <c r="AL26" s="27" t="n"/>
+      <c r="AM26" s="27" t="n"/>
+      <c r="AN26" s="27" t="n"/>
+      <c r="AO26" s="27" t="n"/>
+      <c r="AP26" s="27" t="n"/>
+      <c r="AQ26" s="27" t="n"/>
+      <c r="AR26" s="27" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Solution design</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="42" t="n"/>
+      <c r="F27" s="42" t="n"/>
+      <c r="H27" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="42" t="n"/>
+      <c r="K27" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="42" t="n"/>
+      <c r="M27" s="42" t="n"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>WL MVP 2: Add HRF based Metrics to dashboard</t>
+        </is>
+      </c>
+      <c r="O27" s="27" t="n"/>
+      <c r="P27" s="27" t="n"/>
+      <c r="Q27" s="27" t="n"/>
+      <c r="R27" s="27" t="n"/>
+      <c r="S27" s="27" t="n"/>
+      <c r="T27" s="27" t="n"/>
+      <c r="U27" s="27" t="n"/>
+      <c r="V27" s="27" t="n"/>
+      <c r="W27" s="27" t="n"/>
+      <c r="X27" s="27" t="n"/>
+      <c r="Y27" s="27" t="n"/>
+      <c r="Z27" s="27" t="n"/>
+      <c r="AA27" s="27" t="n"/>
+      <c r="AB27" s="27" t="n"/>
+      <c r="AC27" s="27" t="n"/>
+      <c r="AD27" s="27" t="n"/>
+      <c r="AE27" s="27" t="n"/>
+      <c r="AF27" s="27" t="n"/>
+      <c r="AG27" s="27" t="n"/>
+      <c r="AH27" s="27" t="n"/>
+      <c r="AI27" s="27" t="n"/>
+      <c r="AJ27" s="27" t="n"/>
+      <c r="AK27" s="27" t="n"/>
+      <c r="AL27" s="27" t="n"/>
+      <c r="AM27" s="27" t="n"/>
+      <c r="AN27" s="27" t="n"/>
+      <c r="AO27" s="27" t="n"/>
+      <c r="AP27" s="27" t="n"/>
+      <c r="AQ27" s="27" t="n"/>
+      <c r="AR27" s="27" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Solution design</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="F28" s="42" t="n"/>
+      <c r="H28" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="42" t="n"/>
+      <c r="J28" s="42" t="n"/>
+      <c r="K28" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="42" t="n"/>
+      <c r="M28" s="42" t="n"/>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>SD Beyond MVP2:  SD Anomaly DATA Detection no 21</t>
+        </is>
+      </c>
+      <c r="O28" s="27" t="n"/>
+      <c r="P28" s="27" t="n"/>
+      <c r="Q28" s="27" t="n"/>
+      <c r="R28" s="27" t="n"/>
+      <c r="S28" s="27" t="n"/>
+      <c r="T28" s="27" t="n"/>
+      <c r="U28" s="27" t="n"/>
+      <c r="V28" s="27" t="n"/>
+      <c r="W28" s="27" t="n"/>
+      <c r="X28" s="27" t="n"/>
+      <c r="Y28" s="27" t="n"/>
+      <c r="Z28" s="27" t="n"/>
+      <c r="AA28" s="27" t="n"/>
+      <c r="AB28" s="27" t="n"/>
+      <c r="AC28" s="27" t="n"/>
+      <c r="AD28" s="27" t="n"/>
+      <c r="AE28" s="27" t="n"/>
+      <c r="AF28" s="27" t="n"/>
+      <c r="AG28" s="27" t="n"/>
+      <c r="AH28" s="27" t="n"/>
+      <c r="AI28" s="27" t="n"/>
+      <c r="AJ28" s="27" t="n"/>
+      <c r="AK28" s="27" t="n"/>
+      <c r="AL28" s="27" t="n"/>
+      <c r="AM28" s="27" t="n"/>
+      <c r="AN28" s="27" t="n"/>
+      <c r="AO28" s="27" t="n"/>
+      <c r="AP28" s="27" t="n"/>
+      <c r="AQ28" s="27" t="n"/>
+      <c r="AR28" s="27" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Solution design</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="42" t="n"/>
+      <c r="F29" s="42" t="n"/>
+      <c r="H29" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="42" t="n"/>
+      <c r="J29" s="42" t="n"/>
+      <c r="K29" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="42" t="n"/>
+      <c r="M29" s="42" t="n"/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>SD Beyond MVP2: Full scope ML+Fusion Model training/deployment pipelines</t>
+        </is>
+      </c>
+      <c r="O29" s="27" t="n"/>
+      <c r="P29" s="27" t="n"/>
+      <c r="Q29" s="27" t="n"/>
+      <c r="R29" s="27" t="n"/>
+      <c r="S29" s="27" t="n"/>
+      <c r="T29" s="27" t="n"/>
+      <c r="U29" s="27" t="n"/>
+      <c r="V29" s="27" t="n"/>
+      <c r="W29" s="27" t="n"/>
+      <c r="X29" s="27" t="n"/>
+      <c r="Y29" s="27" t="n"/>
+      <c r="Z29" s="27" t="n"/>
+      <c r="AA29" s="27" t="n"/>
+      <c r="AB29" s="27" t="n"/>
+      <c r="AC29" s="27" t="n"/>
+      <c r="AD29" s="27" t="n"/>
+      <c r="AE29" s="27" t="n"/>
+      <c r="AF29" s="27" t="n"/>
+      <c r="AG29" s="27" t="n"/>
+      <c r="AH29" s="27" t="n"/>
+      <c r="AI29" s="27" t="n"/>
+      <c r="AJ29" s="27" t="n"/>
+      <c r="AK29" s="27" t="n"/>
+      <c r="AL29" s="27" t="n"/>
+      <c r="AM29" s="27" t="n"/>
+      <c r="AN29" s="27" t="n"/>
+      <c r="AO29" s="27" t="n"/>
+      <c r="AP29" s="27" t="n"/>
+      <c r="AQ29" s="27" t="n"/>
+      <c r="AR29" s="27" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-19560</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="42" t="n"/>
+      <c r="F30" s="42" t="n"/>
+      <c r="H30" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="42" t="n"/>
+      <c r="J30" s="42" t="n"/>
+      <c r="K30" s="42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L30" s="42" t="n"/>
+      <c r="M30" s="42" t="n"/>
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>WL MVP1: Extend analytics infrastructure  no 11</t>
+        </is>
+      </c>
+      <c r="O30" s="27" t="n"/>
+      <c r="P30" s="27" t="n"/>
+      <c r="Q30" s="27" t="n"/>
+      <c r="R30" s="27" t="n"/>
+      <c r="S30" s="27" t="n"/>
+      <c r="T30" s="27" t="n"/>
+      <c r="U30" s="27" t="n"/>
+      <c r="V30" s="27" t="n"/>
+      <c r="W30" s="27" t="n"/>
+      <c r="X30" s="27" t="n"/>
+      <c r="Y30" s="27" t="n"/>
+      <c r="Z30" s="27" t="n"/>
+      <c r="AA30" s="27" t="n"/>
+      <c r="AB30" s="27" t="n"/>
+      <c r="AC30" s="27" t="n"/>
+      <c r="AD30" s="27" t="n"/>
+      <c r="AE30" s="27" t="n"/>
+      <c r="AF30" s="27" t="n"/>
+      <c r="AG30" s="27" t="n"/>
+      <c r="AH30" s="27" t="n"/>
+      <c r="AI30" s="27" t="n"/>
+      <c r="AJ30" s="27" t="n"/>
+      <c r="AK30" s="27" t="n"/>
+      <c r="AL30" s="27" t="n"/>
+      <c r="AM30" s="27" t="n"/>
+      <c r="AN30" s="27" t="n"/>
+      <c r="AO30" s="27" t="n"/>
+      <c r="AP30" s="27" t="n"/>
+      <c r="AQ30" s="27" t="n"/>
+      <c r="AR30" s="27" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-19560</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="42" t="n"/>
+      <c r="H31" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="42" t="n"/>
+      <c r="J31" s="42" t="n"/>
+      <c r="K31" s="42" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L31" s="42" t="n"/>
+      <c r="M31" s="42" t="n"/>
+      <c r="N31" s="20" t="inlineStr">
+        <is>
+          <t>WL MVP1.1: E2E testing  (rest of 1.0 test drives)</t>
+        </is>
+      </c>
+      <c r="O31" s="27" t="n"/>
+      <c r="P31" s="27" t="n"/>
+      <c r="Q31" s="27" t="n"/>
+      <c r="R31" s="27" t="n"/>
+      <c r="S31" s="27" t="n"/>
+      <c r="T31" s="27" t="n"/>
+      <c r="U31" s="27" t="n"/>
+      <c r="V31" s="27" t="n"/>
+      <c r="W31" s="27" t="n"/>
+      <c r="X31" s="27" t="n"/>
+      <c r="Y31" s="27" t="n"/>
+      <c r="Z31" s="27" t="n"/>
+      <c r="AA31" s="27" t="n"/>
+      <c r="AB31" s="27" t="n"/>
+      <c r="AC31" s="27" t="n"/>
+      <c r="AD31" s="27" t="n"/>
+      <c r="AE31" s="27" t="n"/>
+      <c r="AF31" s="27" t="n"/>
+      <c r="AG31" s="27" t="n"/>
+      <c r="AH31" s="27" t="n"/>
+      <c r="AI31" s="27" t="n"/>
+      <c r="AJ31" s="27" t="n"/>
+      <c r="AK31" s="27" t="n"/>
+      <c r="AL31" s="27" t="n"/>
+      <c r="AM31" s="27" t="n"/>
+      <c r="AN31" s="27" t="n"/>
+      <c r="AO31" s="27" t="n"/>
+      <c r="AP31" s="27" t="n"/>
+      <c r="AQ31" s="27" t="n"/>
+      <c r="AR31" s="27" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H32" s="42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I32" s="42" t="n"/>
+      <c r="J32" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L32" s="42" t="n"/>
+      <c r="M32" s="42" t="n"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WL MVP 1.1 + 1.2: EV Data Quality Monitoring Framework no 18 :  Continuation from 2025 </t>
+        </is>
+      </c>
+      <c r="O32" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P32" s="27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q32" s="27" t="n"/>
+      <c r="R32" s="27" t="n"/>
+      <c r="S32" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T32" s="27" t="n"/>
+      <c r="U32" s="27" t="n"/>
+      <c r="V32" s="27" t="n"/>
+      <c r="W32" s="27" t="n"/>
+      <c r="X32" s="27" t="n"/>
+      <c r="Y32" s="27" t="n"/>
+      <c r="Z32" s="27" t="n"/>
+      <c r="AA32" s="27" t="n"/>
+      <c r="AB32" s="27" t="n"/>
+      <c r="AC32" s="27" t="n"/>
+      <c r="AD32" s="27" t="n"/>
+      <c r="AE32" s="27" t="n"/>
+      <c r="AF32" s="27" t="n"/>
+      <c r="AG32" s="27" t="n"/>
+      <c r="AH32" s="27" t="n"/>
+      <c r="AI32" s="27" t="n"/>
+      <c r="AJ32" s="27" t="n"/>
+      <c r="AK32" s="27" t="n"/>
+      <c r="AL32" s="27" t="n"/>
+      <c r="AM32" s="27" t="n"/>
+      <c r="AN32" s="27" t="n"/>
+      <c r="AO32" s="27" t="n"/>
+      <c r="AP32" s="27" t="n"/>
+      <c r="AQ32" s="27" t="n"/>
+      <c r="AR32" s="27" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="42" t="n"/>
+      <c r="J33" s="42" t="n"/>
+      <c r="K33" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="42" t="n"/>
+      <c r="M33" s="42" t="n"/>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>WL MVP1.2: EV Metrics Data Model Extension</t>
+        </is>
+      </c>
+      <c r="O33" s="27" t="n"/>
+      <c r="P33" s="27" t="n"/>
+      <c r="Q33" s="27" t="n"/>
+      <c r="R33" s="27" t="n"/>
+      <c r="S33" s="27" t="n"/>
+      <c r="T33" s="27" t="n"/>
+      <c r="U33" s="27" t="n"/>
+      <c r="V33" s="27" t="n"/>
+      <c r="W33" s="27" t="n"/>
+      <c r="X33" s="27" t="n"/>
+      <c r="Y33" s="27" t="n"/>
+      <c r="Z33" s="27" t="n"/>
+      <c r="AA33" s="27" t="n"/>
+      <c r="AB33" s="27" t="n"/>
+      <c r="AC33" s="27" t="n"/>
+      <c r="AD33" s="27" t="n"/>
+      <c r="AE33" s="27" t="n"/>
+      <c r="AF33" s="27" t="n"/>
+      <c r="AG33" s="27" t="n"/>
+      <c r="AH33" s="27" t="n"/>
+      <c r="AI33" s="27" t="n"/>
+      <c r="AJ33" s="27" t="n"/>
+      <c r="AK33" s="27" t="n"/>
+      <c r="AL33" s="27" t="n"/>
+      <c r="AM33" s="27" t="n"/>
+      <c r="AN33" s="27" t="n"/>
+      <c r="AO33" s="27" t="n"/>
+      <c r="AP33" s="27" t="n"/>
+      <c r="AQ33" s="27" t="n"/>
+      <c r="AR33" s="27" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="42" t="n"/>
+      <c r="J34" s="42" t="n"/>
+      <c r="K34" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="42" t="n"/>
+      <c r="M34" s="42" t="n"/>
+      <c r="N34" s="18" t="inlineStr">
+        <is>
+          <t>WL MVP 1.2: EV Metrics Dashboard Extension</t>
+        </is>
+      </c>
+      <c r="O34" s="27" t="n"/>
+      <c r="P34" s="27" t="n"/>
+      <c r="Q34" s="27" t="n"/>
+      <c r="R34" s="27" t="n"/>
+      <c r="S34" s="27" t="n"/>
+      <c r="T34" s="27" t="n"/>
+      <c r="U34" s="27" t="n"/>
+      <c r="V34" s="27" t="n"/>
+      <c r="W34" s="27" t="n"/>
+      <c r="X34" s="27" t="n"/>
+      <c r="Y34" s="27" t="n"/>
+      <c r="Z34" s="27" t="n"/>
+      <c r="AA34" s="27" t="n"/>
+      <c r="AB34" s="27" t="n"/>
+      <c r="AC34" s="27" t="n"/>
+      <c r="AD34" s="27" t="n"/>
+      <c r="AE34" s="27" t="n"/>
+      <c r="AF34" s="27" t="n"/>
+      <c r="AG34" s="27" t="n"/>
+      <c r="AH34" s="27" t="n"/>
+      <c r="AI34" s="27" t="n"/>
+      <c r="AJ34" s="27" t="n"/>
+      <c r="AK34" s="27" t="n"/>
+      <c r="AL34" s="27" t="n"/>
+      <c r="AM34" s="27" t="n"/>
+      <c r="AN34" s="27" t="n"/>
+      <c r="AO34" s="27" t="n"/>
+      <c r="AP34" s="21" t="n"/>
+      <c r="AQ34" s="27" t="n"/>
+      <c r="AR34" s="27" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="42" t="n"/>
+      <c r="F35" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="42" t="n"/>
+      <c r="J35" s="42" t="n"/>
+      <c r="K35" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="42" t="n"/>
+      <c r="M35" s="42" t="n"/>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>WL MVP1.2: Ingestion of third-party data (Fisker &amp; Dimo)</t>
+        </is>
+      </c>
+      <c r="O35" s="27" t="n"/>
+      <c r="P35" s="27" t="n"/>
+      <c r="Q35" s="27" t="n"/>
+      <c r="R35" s="27" t="n"/>
+      <c r="S35" s="27" t="n"/>
+      <c r="T35" s="27" t="n"/>
+      <c r="U35" s="27" t="n"/>
+      <c r="V35" s="27" t="n"/>
+      <c r="W35" s="27" t="n"/>
+      <c r="X35" s="27" t="n"/>
+      <c r="Y35" s="27" t="n"/>
+      <c r="Z35" s="27" t="n"/>
+      <c r="AA35" s="27" t="n"/>
+      <c r="AB35" s="27" t="n"/>
+      <c r="AC35" s="27" t="n"/>
+      <c r="AD35" s="27" t="n"/>
+      <c r="AE35" s="21" t="n"/>
+      <c r="AF35" s="27" t="n"/>
+      <c r="AG35" s="27" t="n"/>
+      <c r="AH35" s="27" t="n"/>
+      <c r="AI35" s="27" t="n"/>
+      <c r="AJ35" s="27" t="n"/>
+      <c r="AK35" s="27" t="n"/>
+      <c r="AL35" s="27" t="n"/>
+      <c r="AM35" s="27" t="n"/>
+      <c r="AN35" s="27" t="n"/>
+      <c r="AO35" s="27" t="n"/>
+      <c r="AP35" s="27" t="n"/>
+      <c r="AQ35" s="27" t="n"/>
+      <c r="AR35" s="27" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>Quality improvements through ML/AI experimentation</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="42" t="n"/>
+      <c r="F36" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="42" t="n"/>
+      <c r="J36" s="42" t="n"/>
+      <c r="K36" s="42" t="n"/>
+      <c r="L36" s="42" t="n"/>
+      <c r="M36" s="42" t="n"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>MVP 1.2: WP 39: Add Consistency Check to Fusion Model Pipeline</t>
+        </is>
+      </c>
+      <c r="O36" s="27" t="n"/>
+      <c r="P36" s="27" t="n"/>
+      <c r="Q36" s="27" t="n"/>
+      <c r="R36" s="27" t="n"/>
+      <c r="S36" s="27" t="n"/>
+      <c r="T36" s="27" t="n"/>
+      <c r="U36" s="27" t="n"/>
+      <c r="V36" s="27" t="n"/>
+      <c r="W36" s="27" t="n"/>
+      <c r="X36" s="27" t="n"/>
+      <c r="Y36" s="27" t="n"/>
+      <c r="Z36" s="27" t="n"/>
+      <c r="AA36" s="27" t="n"/>
+      <c r="AB36" s="27" t="n"/>
+      <c r="AC36" s="27" t="n"/>
+      <c r="AD36" s="27" t="n"/>
+      <c r="AE36" s="21" t="n"/>
+      <c r="AF36" s="27" t="n"/>
+      <c r="AG36" s="27" t="n"/>
+      <c r="AH36" s="27" t="n"/>
+      <c r="AI36" s="27" t="n"/>
+      <c r="AJ36" s="27" t="n"/>
+      <c r="AK36" s="27" t="n"/>
+      <c r="AL36" s="27" t="n"/>
+      <c r="AM36" s="27" t="n"/>
+      <c r="AN36" s="27" t="n"/>
+      <c r="AO36" s="27" t="n"/>
+      <c r="AP36" s="27" t="n"/>
+      <c r="AQ36" s="27" t="n"/>
+      <c r="AR36" s="27" t="n"/>
+      <c r="AS36" s="27" t="inlineStr">
+        <is>
+          <t>WL MVP 1.2: Feature generation capability and process</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>Quality improvements through ML/AI experimentation</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="42" t="n"/>
+      <c r="F37" s="14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H37" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="42" t="n"/>
+      <c r="J37" s="27" t="n"/>
+      <c r="K37" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="42" t="n"/>
+      <c r="M37" s="42" t="n"/>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>WL MVP 1.2: Minimal scope of training/deployment pipelines</t>
+        </is>
+      </c>
+      <c r="O37" s="27" t="n"/>
+      <c r="P37" s="27" t="n"/>
+      <c r="Q37" s="27" t="n"/>
+      <c r="R37" s="27" t="n"/>
+      <c r="S37" s="27" t="n"/>
+      <c r="T37" s="27" t="n"/>
+      <c r="U37" s="27" t="n"/>
+      <c r="V37" s="27" t="n"/>
+      <c r="W37" s="27" t="n"/>
+      <c r="X37" s="27" t="n"/>
+      <c r="Y37" s="27" t="n"/>
+      <c r="Z37" s="27" t="n"/>
+      <c r="AA37" s="27" t="n"/>
+      <c r="AB37" s="27" t="n"/>
+      <c r="AC37" s="27" t="n"/>
+      <c r="AD37" s="27" t="n"/>
+      <c r="AE37" s="27" t="n"/>
+      <c r="AF37" s="21" t="n"/>
+      <c r="AG37" s="21" t="n"/>
+      <c r="AH37" s="27" t="n"/>
+      <c r="AI37" s="27" t="n"/>
+      <c r="AJ37" s="27" t="n"/>
+      <c r="AK37" s="27" t="n"/>
+      <c r="AL37" s="27" t="n"/>
+      <c r="AM37" s="27" t="n"/>
+      <c r="AN37" s="27" t="n"/>
+      <c r="AO37" s="27" t="n"/>
+      <c r="AP37" s="27" t="n"/>
+      <c r="AQ37" s="27" t="n"/>
+      <c r="AR37" s="27" t="n"/>
+      <c r="AS37" s="27" t="inlineStr">
+        <is>
+          <t>WL MVP1.2: Define process to create prod-grade Fusion Model + create the first prod-grade version</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D38" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="42" t="n"/>
+      <c r="F38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J38" s="27" t="n"/>
+      <c r="K38" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="42" t="n"/>
+      <c r="M38" s="42" t="n"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>WL MVP 1.2: Feature generation capability and process</t>
+        </is>
+      </c>
+      <c r="O38" s="27" t="n"/>
+      <c r="P38" s="27" t="n"/>
+      <c r="Q38" s="27" t="n"/>
+      <c r="R38" s="27" t="n"/>
+      <c r="S38" s="27" t="n"/>
+      <c r="T38" s="27" t="n"/>
+      <c r="U38" s="27" t="n"/>
+      <c r="V38" s="27" t="n"/>
+      <c r="W38" s="27" t="n"/>
+      <c r="X38" s="27" t="n"/>
+      <c r="Y38" s="27" t="n"/>
+      <c r="Z38" s="27" t="n"/>
+      <c r="AA38" s="27" t="n"/>
+      <c r="AB38" s="27" t="n"/>
+      <c r="AC38" s="27" t="n"/>
+      <c r="AD38" s="27" t="n"/>
+      <c r="AE38" s="27" t="n"/>
+      <c r="AF38" s="21" t="n"/>
+      <c r="AG38" s="21" t="n"/>
+      <c r="AH38" s="27" t="n"/>
+      <c r="AI38" s="27" t="n"/>
+      <c r="AJ38" s="27" t="n"/>
+      <c r="AK38" s="27" t="n"/>
+      <c r="AL38" s="27" t="n"/>
+      <c r="AM38" s="27" t="n"/>
+      <c r="AN38" s="27" t="n"/>
+      <c r="AO38" s="27" t="n"/>
+      <c r="AP38" s="27" t="n"/>
+      <c r="AQ38" s="27" t="n"/>
+      <c r="AR38" s="27" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="42" t="n"/>
+      <c r="F39" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="42" t="n"/>
+      <c r="J39" s="27" t="n"/>
+      <c r="K39" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="42" t="n"/>
+      <c r="M39" s="42" t="n"/>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>WL MVP1.2: Define process to create prod-grade Fusion Model + create the first prod-grade version</t>
+        </is>
+      </c>
+      <c r="O39" s="27" t="n"/>
+      <c r="P39" s="27" t="n"/>
+      <c r="Q39" s="27" t="n"/>
+      <c r="R39" s="27" t="n"/>
+      <c r="S39" s="27" t="n"/>
+      <c r="T39" s="27" t="n"/>
+      <c r="U39" s="27" t="n"/>
+      <c r="V39" s="27" t="n"/>
+      <c r="W39" s="27" t="n"/>
+      <c r="X39" s="27" t="n"/>
+      <c r="Y39" s="27" t="n"/>
+      <c r="Z39" s="27" t="n"/>
+      <c r="AA39" s="27" t="n"/>
+      <c r="AB39" s="27" t="n"/>
+      <c r="AC39" s="27" t="n"/>
+      <c r="AD39" s="27" t="n"/>
+      <c r="AE39" s="27" t="n"/>
+      <c r="AF39" s="27" t="n"/>
+      <c r="AG39" s="27" t="n"/>
+      <c r="AH39" s="27" t="n"/>
+      <c r="AI39" s="27" t="n"/>
+      <c r="AJ39" s="27" t="n"/>
+      <c r="AK39" s="27" t="n"/>
+      <c r="AL39" s="27" t="n"/>
+      <c r="AM39" s="27" t="n"/>
+      <c r="AN39" s="27" t="n"/>
+      <c r="AO39" s="27" t="n"/>
+      <c r="AP39" s="27" t="n"/>
+      <c r="AQ39" s="21" t="n"/>
+      <c r="AR39" s="27" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D40" s="27" t="n"/>
+      <c r="E40" s="42" t="n"/>
+      <c r="F40" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="42" t="n"/>
+      <c r="J40" s="42" t="n"/>
+      <c r="K40" s="42" t="n"/>
+      <c r="L40" s="42" t="n"/>
+      <c r="M40" s="42" t="n"/>
+      <c r="N40" s="33" t="inlineStr">
+        <is>
+          <t>MVP E2E 1.2 Testing</t>
+        </is>
+      </c>
+      <c r="O40" s="27" t="n"/>
+      <c r="P40" s="27" t="n"/>
+      <c r="Q40" s="27" t="n"/>
+      <c r="R40" s="27" t="n"/>
+      <c r="S40" s="27" t="n"/>
+      <c r="T40" s="27" t="n"/>
+      <c r="U40" s="27" t="n"/>
+      <c r="V40" s="27" t="n"/>
+      <c r="W40" s="27" t="n"/>
+      <c r="X40" s="27" t="n"/>
+      <c r="Y40" s="27" t="n"/>
+      <c r="Z40" s="27" t="n"/>
+      <c r="AA40" s="27" t="n"/>
+      <c r="AB40" s="27" t="n"/>
+      <c r="AC40" s="27" t="n"/>
+      <c r="AD40" s="27" t="n"/>
+      <c r="AE40" s="27" t="n"/>
+      <c r="AF40" s="27" t="n"/>
+      <c r="AG40" s="27" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D41" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="42" t="n"/>
+      <c r="F41" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="42" t="n"/>
+      <c r="M41" s="42" t="n"/>
+      <c r="N41" s="34" t="inlineStr">
+        <is>
+          <t>WL MVP 1.2: Support Charm with the integration testing</t>
+        </is>
+      </c>
+      <c r="O41" s="27" t="n"/>
+      <c r="P41" s="27" t="n"/>
+      <c r="Q41" s="27" t="n"/>
+      <c r="R41" s="27" t="n"/>
+      <c r="S41" s="27" t="n"/>
+      <c r="T41" s="27" t="n"/>
+      <c r="U41" s="27" t="n"/>
+      <c r="V41" s="27" t="n"/>
+      <c r="W41" s="27" t="n"/>
+      <c r="X41" s="27" t="n"/>
+      <c r="Y41" s="27" t="n"/>
+      <c r="Z41" s="27" t="n"/>
+      <c r="AA41" s="27" t="n"/>
+      <c r="AB41" s="27" t="n"/>
+      <c r="AC41" s="27" t="n"/>
+      <c r="AD41" s="27" t="n"/>
+      <c r="AE41" s="27" t="n"/>
+      <c r="AF41" s="27" t="n"/>
+      <c r="AG41" s="27" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D42" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="42" t="n"/>
+      <c r="F42" s="42" t="n"/>
+      <c r="G42" s="42" t="n"/>
+      <c r="H42" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="27" t="n"/>
+      <c r="K42" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="42" t="n"/>
+      <c r="M42" s="42" t="n"/>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>WL MVP2 Data collection - external fleets - AUI</t>
+        </is>
+      </c>
+      <c r="O42" s="27" t="n"/>
+      <c r="P42" s="27" t="n"/>
+      <c r="Q42" s="27" t="n"/>
+      <c r="R42" s="27" t="n"/>
+      <c r="S42" s="27" t="n"/>
+      <c r="T42" s="27" t="n"/>
+      <c r="U42" s="27" t="n"/>
+      <c r="V42" s="27" t="n"/>
+      <c r="W42" s="27" t="n"/>
+      <c r="X42" s="27" t="n"/>
+      <c r="Y42" s="27" t="n"/>
+      <c r="Z42" s="27" t="n"/>
+      <c r="AA42" s="27" t="n"/>
+      <c r="AB42" s="27" t="n"/>
+      <c r="AC42" s="27" t="n"/>
+      <c r="AD42" s="27" t="n"/>
+      <c r="AE42" s="27" t="n"/>
+      <c r="AF42" s="27" t="n"/>
+      <c r="AG42" s="27" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>Quality improvements through ML/AI experimentation</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D43" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="42" t="n"/>
+      <c r="F43" s="42" t="n"/>
+      <c r="G43" s="42" t="n"/>
+      <c r="H43" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="42" t="n"/>
+      <c r="K43" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="42" t="n"/>
+      <c r="M43" s="42" t="n"/>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>WL MVP2: In drive self-correction support</t>
+        </is>
+      </c>
+      <c r="O43" s="27" t="n"/>
+      <c r="P43" s="27" t="n"/>
+      <c r="Q43" s="27" t="n"/>
+      <c r="R43" s="27" t="n"/>
+      <c r="S43" s="27" t="n"/>
+      <c r="T43" s="27" t="n"/>
+      <c r="U43" s="27" t="n"/>
+      <c r="V43" s="27" t="n"/>
+      <c r="W43" s="27" t="n"/>
+      <c r="X43" s="27" t="n"/>
+      <c r="Y43" s="27" t="n"/>
+      <c r="Z43" s="27" t="n"/>
+      <c r="AA43" s="27" t="n"/>
+      <c r="AB43" s="27" t="n"/>
+      <c r="AC43" s="27" t="n"/>
+      <c r="AD43" s="27" t="n"/>
+      <c r="AE43" s="27" t="n"/>
+      <c r="AF43" s="27" t="n"/>
+      <c r="AG43" s="27" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="42" t="n"/>
+      <c r="F44" s="42" t="n"/>
+      <c r="G44" s="42" t="n"/>
+      <c r="H44" s="42" t="n"/>
+      <c r="I44" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="42" t="n"/>
+      <c r="K44" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="42" t="n"/>
+      <c r="M44" s="42" t="n"/>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>WL MVP2: no 15 Extend analytics infrastructure semantically undefin attributes</t>
+        </is>
+      </c>
+      <c r="O44" s="27" t="n"/>
+      <c r="P44" s="27" t="n"/>
+      <c r="Q44" s="27" t="n"/>
+      <c r="R44" s="27" t="n"/>
+      <c r="S44" s="27" t="n"/>
+      <c r="T44" s="27" t="n"/>
+      <c r="U44" s="27" t="n"/>
+      <c r="V44" s="27" t="n"/>
+      <c r="W44" s="27" t="n"/>
+      <c r="X44" s="27" t="n"/>
+      <c r="Y44" s="27" t="n"/>
+      <c r="Z44" s="27" t="n"/>
+      <c r="AA44" s="27" t="n"/>
+      <c r="AB44" s="27" t="n"/>
+      <c r="AC44" s="27" t="n"/>
+      <c r="AD44" s="27" t="n"/>
+      <c r="AE44" s="21" t="n"/>
+      <c r="AF44" s="27" t="n"/>
+      <c r="AG44" s="27" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D45" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="42" t="n"/>
+      <c r="F45" s="42" t="n"/>
+      <c r="G45" s="42" t="n"/>
+      <c r="H45" s="42" t="n"/>
+      <c r="I45" s="42" t="n"/>
+      <c r="J45" s="35" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="K45" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="42" t="n"/>
+      <c r="M45" s="42" t="n"/>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>WL MVP2 : Add HRF based Metrics to dashboard</t>
+        </is>
+      </c>
+      <c r="O45" s="27" t="n"/>
+      <c r="P45" s="27" t="n"/>
+      <c r="Q45" s="27" t="n"/>
+      <c r="R45" s="27" t="n"/>
+      <c r="S45" s="27" t="n"/>
+      <c r="T45" s="27" t="n"/>
+      <c r="U45" s="27" t="n"/>
+      <c r="V45" s="27" t="n"/>
+      <c r="W45" s="27" t="n"/>
+      <c r="X45" s="27" t="n"/>
+      <c r="Y45" s="27" t="n"/>
+      <c r="Z45" s="27" t="n"/>
+      <c r="AA45" s="27" t="n"/>
+      <c r="AB45" s="27" t="n"/>
+      <c r="AC45" s="27" t="n"/>
+      <c r="AD45" s="27" t="n"/>
+      <c r="AE45" s="27" t="n"/>
+      <c r="AF45" s="27" t="n"/>
+      <c r="AG45" s="27" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>GOSDK-170623</t>
+        </is>
+      </c>
+      <c r="D46" s="27" t="n"/>
+      <c r="E46" s="42" t="n"/>
+      <c r="F46" s="42" t="n"/>
+      <c r="G46" s="42" t="n"/>
+      <c r="H46" s="42" t="n"/>
+      <c r="I46" s="42" t="n"/>
+      <c r="J46" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K46" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="42" t="n"/>
+      <c r="M46" s="42" t="n"/>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WL MVP2: E2E testing </t>
+        </is>
+      </c>
+      <c r="O46" s="27" t="n"/>
+      <c r="P46" s="27" t="n"/>
+      <c r="Q46" s="27" t="n"/>
+      <c r="R46" s="27" t="n"/>
+      <c r="S46" s="27" t="n"/>
+      <c r="T46" s="27" t="n"/>
+      <c r="U46" s="27" t="n"/>
+      <c r="V46" s="27" t="n"/>
+      <c r="W46" s="27" t="n"/>
+      <c r="X46" s="27" t="n"/>
+      <c r="Y46" s="27" t="n"/>
+      <c r="Z46" s="27" t="n"/>
+      <c r="AA46" s="27" t="n"/>
+      <c r="AB46" s="27" t="n"/>
+      <c r="AC46" s="27" t="n"/>
+      <c r="AD46" s="27" t="n"/>
+      <c r="AE46" s="27" t="n"/>
+      <c r="AF46" s="27" t="n"/>
+      <c r="AG46" s="27" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="27" t="n"/>
+      <c r="E47" s="42" t="n"/>
+      <c r="F47" s="42" t="n"/>
+      <c r="G47" s="42" t="n"/>
+      <c r="H47" s="42" t="n"/>
+      <c r="I47" s="42" t="n"/>
+      <c r="J47" s="42" t="n"/>
+      <c r="K47" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="42" t="n"/>
+      <c r="M47" s="42" t="n"/>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>BEYOND WL MVP2:  Full scope of  trainig/deployment pipelines</t>
+        </is>
+      </c>
+      <c r="O47" s="27" t="n"/>
+      <c r="P47" s="27" t="n"/>
+      <c r="Q47" s="27" t="n"/>
+      <c r="R47" s="27" t="n"/>
+      <c r="S47" s="27" t="n"/>
+      <c r="T47" s="27" t="n"/>
+      <c r="U47" s="27" t="n"/>
+      <c r="V47" s="27" t="n"/>
+      <c r="W47" s="27" t="n"/>
+      <c r="X47" s="27" t="n"/>
+      <c r="Y47" s="27" t="n"/>
+      <c r="Z47" s="27" t="n"/>
+      <c r="AA47" s="27" t="n"/>
+      <c r="AB47" s="27" t="n"/>
+      <c r="AC47" s="27" t="n"/>
+      <c r="AD47" s="27" t="n"/>
+      <c r="AE47" s="27" t="n"/>
+      <c r="AF47" s="21" t="n"/>
+      <c r="AG47" s="21" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="27" t="n"/>
+      <c r="E48" s="42" t="n"/>
+      <c r="F48" s="42" t="n"/>
+      <c r="G48" s="42" t="n"/>
+      <c r="H48" s="42" t="n"/>
+      <c r="I48" s="42" t="n"/>
+      <c r="J48" s="42" t="n"/>
+      <c r="K48" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="42" t="n"/>
+      <c r="M48" s="42" t="n"/>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>BEYOND WL MVP2: EV Data Collection for White-label EV routing [ nice to have AUI + NK1] - Jira (no jira ticket yet)</t>
+        </is>
+      </c>
+      <c r="O48" s="27" t="n"/>
+      <c r="P48" s="27" t="n"/>
+      <c r="Q48" s="27" t="n"/>
+      <c r="R48" s="27" t="n"/>
+      <c r="S48" s="27" t="n"/>
+      <c r="T48" s="27" t="n"/>
+      <c r="U48" s="27" t="n"/>
+      <c r="V48" s="27" t="n"/>
+      <c r="W48" s="27" t="n"/>
+      <c r="X48" s="27" t="n"/>
+      <c r="Y48" s="27" t="n"/>
+      <c r="Z48" s="27" t="n"/>
+      <c r="AA48" s="27" t="n"/>
+      <c r="AB48" s="27" t="n"/>
+      <c r="AC48" s="27" t="n"/>
+      <c r="AD48" s="27" t="n"/>
+      <c r="AE48" s="27" t="n"/>
+      <c r="AF48" s="27" t="n"/>
+      <c r="AG48" s="27" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Self-Service ML EV Range - Phase 1</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>White Label</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="27" t="n"/>
+      <c r="E49" s="42" t="n"/>
+      <c r="F49" s="42" t="n"/>
+      <c r="G49" s="42" t="n"/>
+      <c r="H49" s="42" t="n"/>
+      <c r="I49" s="42" t="n"/>
+      <c r="J49" s="42" t="n"/>
+      <c r="K49" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="42" t="n"/>
+      <c r="M49" s="42" t="n"/>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>BEYOND WL MVP2: Make use of data collected in free-driving mode</t>
+        </is>
+      </c>
+      <c r="O49" s="27" t="n"/>
+      <c r="P49" s="27" t="n"/>
+      <c r="Q49" s="27" t="n"/>
+      <c r="R49" s="27" t="n"/>
+      <c r="S49" s="27" t="n"/>
+      <c r="T49" s="27" t="n"/>
+      <c r="U49" s="27" t="n"/>
+      <c r="V49" s="27" t="n"/>
+      <c r="W49" s="27" t="n"/>
+      <c r="X49" s="27" t="n"/>
+      <c r="Y49" s="27" t="n"/>
+      <c r="Z49" s="27" t="n"/>
+      <c r="AA49" s="27" t="n"/>
+      <c r="AB49" s="27" t="n"/>
+      <c r="AC49" s="27" t="n"/>
+      <c r="AD49" s="27" t="n"/>
+      <c r="AE49" s="23" t="n"/>
+      <c r="AF49" s="27" t="n"/>
+      <c r="AG49" s="27" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="27" t="n"/>
+      <c r="B50" s="27" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="27" t="n"/>
+      <c r="E50" s="42" t="n"/>
+      <c r="F50" s="42" t="n"/>
+      <c r="G50" s="42" t="n"/>
+      <c r="H50" s="42" t="n"/>
+      <c r="I50" s="42" t="n"/>
+      <c r="J50" s="42" t="n"/>
+      <c r="K50" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="42" t="n"/>
+      <c r="M50" s="42" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="27" t="n"/>
+      <c r="P50" s="27" t="n"/>
+      <c r="Q50" s="27" t="n"/>
+      <c r="R50" s="27" t="n"/>
+      <c r="S50" s="27" t="n"/>
+      <c r="T50" s="27" t="n"/>
+      <c r="U50" s="27" t="n"/>
+      <c r="V50" s="27" t="n"/>
+      <c r="W50" s="27" t="n"/>
+      <c r="X50" s="27" t="n"/>
+      <c r="Y50" s="27" t="n"/>
+      <c r="Z50" s="27" t="n"/>
+      <c r="AA50" s="27" t="n"/>
+      <c r="AB50" s="27" t="n"/>
+      <c r="AC50" s="27" t="n"/>
+      <c r="AD50" s="27" t="n"/>
+      <c r="AE50" s="23" t="n"/>
+      <c r="AF50" s="27" t="n"/>
+      <c r="AG50" s="27" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="27" t="n"/>
+      <c r="B51" s="27" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="27" t="n"/>
+      <c r="E51" s="42" t="n"/>
+      <c r="F51" s="42" t="n"/>
+      <c r="G51" s="42" t="n"/>
+      <c r="H51" s="42" t="n"/>
+      <c r="I51" s="42" t="n"/>
+      <c r="J51" s="42" t="n"/>
+      <c r="K51" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="42" t="n"/>
+      <c r="M51" s="42" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="27" t="n"/>
+      <c r="P51" s="27" t="n"/>
+      <c r="Q51" s="27" t="n"/>
+      <c r="R51" s="27" t="n"/>
+      <c r="S51" s="27" t="n"/>
+      <c r="T51" s="27" t="n"/>
+      <c r="U51" s="27" t="n"/>
+      <c r="V51" s="27" t="n"/>
+      <c r="W51" s="27" t="n"/>
+      <c r="X51" s="27" t="n"/>
+      <c r="Y51" s="27" t="n"/>
+      <c r="Z51" s="27" t="n"/>
+      <c r="AA51" s="27" t="n"/>
+      <c r="AB51" s="27" t="n"/>
+      <c r="AC51" s="27" t="n"/>
+      <c r="AD51" s="27" t="n"/>
+      <c r="AE51" s="23" t="n"/>
+      <c r="AF51" s="23" t="n"/>
+      <c r="AG51" s="23" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="n"/>
+      <c r="B52" s="27" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="27" t="n"/>
+      <c r="E52" s="42" t="n"/>
+      <c r="F52" s="42" t="n"/>
+      <c r="G52" s="42" t="n"/>
+      <c r="H52" s="42" t="n"/>
+      <c r="I52" s="42" t="n"/>
+      <c r="J52" s="42" t="n"/>
+      <c r="K52" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="42" t="n"/>
+      <c r="M52" s="42" t="n"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="27" t="n"/>
+      <c r="P52" s="27" t="n"/>
+      <c r="Q52" s="27" t="n"/>
+      <c r="R52" s="27" t="n"/>
+      <c r="S52" s="27" t="n"/>
+      <c r="T52" s="27" t="n"/>
+      <c r="U52" s="27" t="n"/>
+      <c r="V52" s="27" t="n"/>
+      <c r="W52" s="27" t="n"/>
+      <c r="X52" s="27" t="n"/>
+      <c r="Y52" s="27" t="n"/>
+      <c r="Z52" s="27" t="n"/>
+      <c r="AA52" s="27" t="n"/>
+      <c r="AB52" s="27" t="n"/>
+      <c r="AC52" s="27" t="n"/>
+      <c r="AD52" s="27" t="n"/>
+      <c r="AE52" s="23" t="n"/>
+      <c r="AF52" s="27" t="n"/>
+      <c r="AG52" s="27" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="n"/>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>Sum of estimated work</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E53" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Management Capacity (Bruto)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="F53" s="36" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G53" s="22" t="n"/>
+      <c r="H53" s="22" t="n"/>
+      <c r="I53" s="22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J53" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="K53" s="38" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="L53" s="38" t="n"/>
+      <c r="M53" s="38" t="n"/>
+      <c r="N53" s="21" t="inlineStr">
+        <is>
+          <t>Should not have worked on this</t>
+        </is>
+      </c>
+      <c r="O53" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Auth &amp; Identity Management</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Analytics</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Real-time Analytics</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Auth &amp; Identity Management</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Quality improvements through ML/AI experimentation</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ML Experimentation</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Real-time Analytics</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
+      <c r="P53" s="39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="23" t="n"/>
+      <c r="AF53" s="23" t="n"/>
+      <c r="AG53" s="23" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="L2:L3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="N15" display="https://tomtom.atlassian.net/browse/NAV-176879" r:id="rId1"/>
+    <hyperlink ref="C16" display="https://tomtom.atlassian.net/browse/NAV-170423" r:id="rId2"/>
+    <hyperlink ref="N16" display="https://tomtom.atlassian.net/browse/NAV-170423" r:id="rId3"/>
+    <hyperlink ref="N17" display="https://tomtom.atlassian.net/browse/NAV-177386" r:id="rId4"/>
+    <hyperlink ref="C18" display="https://tomtom.atlassian.net/browse/NAV-180094" r:id="rId5"/>
+    <hyperlink ref="N18" display="https://tomtom.atlassian.net/browse/NAV-180094" r:id="rId6"/>
+    <hyperlink ref="N19" display="https://tomtom.atlassian.net/browse/NAV-186786" r:id="rId7"/>
+    <hyperlink ref="N20" display="https://tomtom.atlassian.net/browse/NAV-197467" r:id="rId8"/>
+    <hyperlink ref="C21" display="https://tomtom.atlassian.net/browse/GOSDK-21982" r:id="rId9"/>
+    <hyperlink ref="N21" display="https://tomtom.atlassian.net/browse/NAV-149249" r:id="rId10"/>
+    <hyperlink ref="N22" display="https://tomtom.atlassian.net/browse/NAV-177386" r:id="rId11"/>
+    <hyperlink ref="N23" display="https://tomtom.atlassian.net/browse/NAV-196231" r:id="rId12"/>
+    <hyperlink ref="C24" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId13"/>
+    <hyperlink ref="N24" display="https://tomtom.atlassian.net/browse/NAV-186952" r:id="rId14"/>
+    <hyperlink ref="C25" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId15"/>
+    <hyperlink ref="N25" display="https://tomtom.atlassian.net/browse/NAV-192701" r:id="rId16"/>
+    <hyperlink ref="C26" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId17"/>
+    <hyperlink ref="N26" display="https://tomtom.atlassian.net/browse/NAV-192703" r:id="rId18"/>
+    <hyperlink ref="C27" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId19"/>
+    <hyperlink ref="N27" display="https://tomtom.atlassian.net/browse/NAV-192835" r:id="rId20"/>
+    <hyperlink ref="C28" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId21"/>
+    <hyperlink ref="N28" display="https://tomtom.atlassian.net/browse/NAV-192704" r:id="rId22"/>
+    <hyperlink ref="C29" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId23"/>
+    <hyperlink ref="N29" display="https://tomtom.atlassian.net/browse/NAV-180190" r:id="rId24"/>
+    <hyperlink ref="C30" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId25"/>
+    <hyperlink ref="N30" display="https://tomtom.atlassian.net/browse/NAV-190211" r:id="rId26"/>
+    <hyperlink ref="C31" display="https://tomtom.atlassian.net/browse/GOSDK-19560" r:id="rId27"/>
+    <hyperlink ref="N31" display="https://tomtom.atlassian.net/browse/NAV-170984" r:id="rId28"/>
+    <hyperlink ref="C32" display="https://tomtom.atlassian.net/browse/GOSDK-19560" r:id="rId29"/>
+    <hyperlink ref="N32" display="https://tomtom.atlassian.net/browse/NAV-178125" r:id="rId30"/>
+    <hyperlink ref="C33" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId31"/>
+    <hyperlink ref="N33" display="https://tomtom.atlassian.net/browse/NAV-180176" r:id="rId32"/>
+    <hyperlink ref="C34" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId33"/>
+    <hyperlink ref="N34" display="https://tomtom.atlassian.net/browse/NAV-192605" r:id="rId34"/>
+    <hyperlink ref="C35" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId35"/>
+    <hyperlink ref="N35" display="https://tomtom.atlassian.net/browse/NAV-186952" r:id="rId36"/>
+    <hyperlink ref="C36" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId37"/>
+    <hyperlink ref="N36" display="https://tomtom.atlassian.net/browse/NAV-192697" r:id="rId38"/>
+    <hyperlink ref="C37" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId39"/>
+    <hyperlink ref="N37" display="https://tomtom.atlassian.net/browse/NAV-192835" r:id="rId40"/>
+    <hyperlink ref="C38" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId41"/>
+    <hyperlink ref="N38" display="https://tomtom.atlassian.net/browse/NAV-181829" r:id="rId42"/>
+    <hyperlink ref="C39" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId43"/>
+    <hyperlink ref="N39" display="https://tomtom.atlassian.net/browse/NAV-192701" r:id="rId44"/>
+    <hyperlink ref="C40" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId45"/>
+    <hyperlink ref="N40" display="https://tomtom.atlassian.net/browse/NAV-192703" r:id="rId46"/>
+    <hyperlink ref="C41" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId47"/>
+    <hyperlink ref="N41" display="https://tomtom.atlassian.net/browse/NAV-197675" r:id="rId48"/>
+    <hyperlink ref="C42" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId49"/>
+    <hyperlink ref="N42" display="https://tomtom.atlassian.net/browse/NAV-186512" r:id="rId50"/>
+    <hyperlink ref="C43" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId51"/>
+    <hyperlink ref="N43" display="https://tomtom.atlassian.net/browse/NAV-192712" r:id="rId52"/>
+    <hyperlink ref="C44" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId53"/>
+    <hyperlink ref="N44" display="https://tomtom.atlassian.net/browse/NAV-188413" r:id="rId54"/>
+    <hyperlink ref="C45" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId55"/>
+    <hyperlink ref="N45" display="https://tomtom.atlassian.net/browse/NAV-171089" r:id="rId56"/>
+    <hyperlink ref="C46" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId57"/>
+    <hyperlink ref="N46" display="https://tomtom.atlassian.net/browse/NAV-192704" r:id="rId58"/>
+    <hyperlink ref="C47" display="https://tomtom.atlassian.net/browse/GOSDK-170623" r:id="rId59"/>
+    <hyperlink ref="N47" display="https://tomtom.atlassian.net/browse/NAV-181832" r:id="rId60"/>
+    <hyperlink ref="N48" display="https://tomtom.atlassian.net/browse/NAV-190211" r:id="rId61"/>
+    <hyperlink ref="N49" display="https://tomtom.atlassian.net/browse/GOSDK-168537" r:id="rId62"/>
+    <hyperlink ref="N50" display="https://tomtom.atlassian.net/browse/NAV-186796" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>